--- a/supabase/functions/prospect-import-preview/test/fixtures/trade_up_ficticio.xlsx
+++ b/supabase/functions/prospect-import-preview/test/fixtures/trade_up_ficticio.xlsx
@@ -857,7 +857,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="e">
         <f>2020+5</f>
       </c>
       <c r="B3" t="str">
@@ -866,7 +866,7 @@
       <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D3">
+      <c r="D3" t="e">
         <f>2020+5</f>
       </c>
       <c r="E3" t="str">
